--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Level</t>
@@ -138,40 +138,46 @@
     <t>1</t>
   </si>
   <si>
+    <t>ems-home</t>
+  </si>
+  <si>
+    <t>patient arrived by EMS/ambulance from home/scene</t>
+  </si>
+  <si>
     <t>ems-gp</t>
   </si>
   <si>
-    <t>EMS from GP</t>
+    <t>patient arrived by EMS/ambulance from general practitioner/outpatient office/community service</t>
   </si>
   <si>
     <t>priv-transport</t>
   </si>
   <si>
-    <t>Private Transportation</t>
+    <t>patient arrived by private transportation from home/scene</t>
   </si>
   <si>
     <t>stroke-center</t>
   </si>
   <si>
-    <t>Stroke Center</t>
+    <t>patient arrived from stroke treating center</t>
   </si>
   <si>
     <t>another-hosp</t>
   </si>
   <si>
-    <t>Another Hospital</t>
+    <t>patient arrived from hospital that is not stroke treating center</t>
   </si>
   <si>
     <t>priv-transport-gp</t>
   </si>
   <si>
-    <t>Private Transportation from GP</t>
+    <t>patient arrived by private transportation from general practitioner/outpatient office/community service</t>
   </si>
   <si>
     <t>in-hospital-stroke</t>
   </si>
   <si>
-    <t>In-Hospital Stroke</t>
+    <t>stroke while hospitalized in another department of the same hospital</t>
   </si>
 </sst>
 </file>
@@ -481,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -570,6 +576,18 @@
       </c>
       <c r="D7" s="2"/>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/stroke-arrival-mode-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/stroke-arrival-mode-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://tecnomod-um.org/CodeSystem/stroke-arrival-mode-cs.</t>
+    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://qualityregistry.org/CodeSystem/stroke-arrival-mode-cs.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-stroke-arrival-mode-cs.xlsx
+++ b/CodeSystem-stroke-arrival-mode-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
